--- a/Grille_projet.xlsx
+++ b/Grille_projet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marce\OneDrive\Desktop\Ecole\5TTI (2025-2026)\info\Web - Mr De Mahieu\projetCUISINE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEED4596-3A3B-4357-B61F-7FCC0819CD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D01E995-DCC5-4332-ADFE-6AAEF05A22B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9F659B29-08EC-4120-BEAF-4D41FF066838}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>BDD</t>
   </si>
@@ -785,43 +785,57 @@
       <c r="A16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="17" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="18" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="14"/>
+      <c r="B19" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="20" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="14"/>
+      <c r="B20" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="22" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="14"/>
+      <c r="B22" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="23" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
@@ -833,7 +847,9 @@
       <c r="A24" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="14"/>
+      <c r="B24" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="25" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
@@ -845,19 +861,25 @@
       <c r="A26" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="14"/>
+      <c r="B26" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="14"/>
+      <c r="B27" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="14"/>
+      <c r="B28" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
@@ -869,31 +891,41 @@
       <c r="A30" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="14"/>
+      <c r="B31" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="32" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="14"/>
+      <c r="B32" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="33" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="14"/>
+      <c r="B33" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="34" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="14"/>
+      <c r="B34" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="35" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
@@ -905,7 +937,9 @@
       <c r="A36" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="14"/>
+      <c r="B36" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="37" spans="1:2" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
